--- a/product_upload/packages/62/file.xlsx
+++ b/product_upload/packages/62/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE .9% + DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-C8BDFE6A5D71</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1018,6 +1028,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>SODIUM ACETATE F.T.V.40mEq</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-25BD5812B77B</t>
         </is>
       </c>
@@ -1041,7 +1056,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1192,6 +1207,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>CLENIL FORTE 250MCG PUFF METERED INHALER</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-2E64A8E26B7B</t>
         </is>
       </c>
@@ -1215,7 +1235,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1374,6 +1394,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>CLAVODAR 1GM F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-14F267D44E47</t>
         </is>
       </c>
@@ -1397,7 +1422,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1556,6 +1581,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>CLORACEF 250MG/5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-6ADBFC0E1826</t>
         </is>
       </c>
@@ -1579,7 +1609,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1738,6 +1768,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>CITANEST 3% DENTAL OCTAPRESSIN CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-C5C120C09365</t>
         </is>
       </c>
@@ -1761,7 +1796,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1916,6 +1951,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>CITALOGEN 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-A367E0ED5224</t>
         </is>
       </c>
@@ -1939,7 +1979,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2094,6 +2134,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>CITALOGEN 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-9BD622E2AAFD</t>
         </is>
       </c>
@@ -2117,7 +2162,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2276,6 +2321,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>CLARITINE 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-95D2CEB34F9B</t>
         </is>
       </c>
@@ -2299,7 +2349,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2450,6 +2500,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>CLARITINE 10MG TAB</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-B288C7D9ECB8</t>
         </is>
       </c>
@@ -2473,7 +2528,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2632,6 +2687,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>CLORACEF 375MG- 5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-06BF63BB4127</t>
         </is>
       </c>
@@ -2655,7 +2715,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2818,6 +2878,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>CONCOR 5 PLUS F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-9F0D5D4495D9</t>
         </is>
       </c>
@@ -2841,7 +2906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2992,6 +3057,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>CONCERTA EXTENDED RELEASE 36MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-4FB17040C1F3</t>
         </is>
       </c>
@@ -3015,7 +3085,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3170,6 +3240,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>CONCERTA EXTENDED RELEASE 18MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-8D4400894D48</t>
         </is>
       </c>
@@ -3193,7 +3268,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3344,6 +3419,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>COBAL 500MCG TAB</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-3A5C64D1EF7C</t>
         </is>
       </c>
@@ -3367,7 +3447,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3518,6 +3598,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>COLI-URINAL effervescent granules</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-6924194B6270</t>
         </is>
       </c>
@@ -3541,7 +3626,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3700,6 +3785,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>CEFPROZ 250MG/5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-6E6084331034</t>
         </is>
       </c>
@@ -3723,7 +3813,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3882,6 +3972,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>CIPROCIN 0.3%</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-4D9C6888D924</t>
         </is>
       </c>
@@ -3905,7 +4000,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4064,6 +4159,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>CIPROMAX 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-834F07294BC8</t>
         </is>
       </c>
@@ -4087,7 +4187,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4238,6 +4338,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>CIPROMAX 750MG TAB</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-49505E374C32</t>
         </is>
       </c>
@@ -4261,7 +4366,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4420,6 +4525,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>CETROTIDE 0.25MG POW. FOR SOLU. FOR INJ.</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-6E39064A8E51</t>
         </is>
       </c>
@@ -4443,7 +4553,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4606,6 +4716,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CHORIOMON 5000 I.U VIAL+AMP OF SOLVENT</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-F944F072A459</t>
         </is>
       </c>
@@ -4629,7 +4744,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4784,6 +4899,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>CHLOROQUINE</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-7C8FD1794B32</t>
         </is>
       </c>
@@ -4807,7 +4927,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4966,6 +5086,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>DAROXIME</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-808328F0CF16</t>
         </is>
       </c>
@@ -4989,7 +5114,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5144,6 +5269,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>DALACIN VAGINAL CREAM 2%</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-8BC12D9D3D06</t>
         </is>
       </c>
@@ -5167,7 +5297,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5326,6 +5456,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>DALACIN T LOTION 1%</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-4247B38BDD2F</t>
         </is>
       </c>
@@ -5349,7 +5484,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5504,6 +5639,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>DERMATIN SOLUTION 1%</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-0F16B9E09DD7</t>
         </is>
       </c>
@@ -5527,7 +5667,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5686,6 +5826,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>DERMATIN CREAM 1%</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-AFE2E3708DE2</t>
         </is>
       </c>
@@ -5709,7 +5854,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5864,6 +6009,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>DERMOVATE OINTMENT 0.05%</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-E4CDF8601C13</t>
         </is>
       </c>
@@ -5887,7 +6037,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6046,6 +6196,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>DECAL B12</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-5C5742D379DC</t>
         </is>
       </c>
@@ -6069,7 +6224,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6224,6 +6379,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>ANTIPLATE 75MG TAB</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-826AE58F0B4D</t>
         </is>
       </c>
@@ -6247,7 +6407,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6402,6 +6562,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>AMLOPINE 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-601D019CF18B</t>
         </is>
       </c>
@@ -6425,7 +6590,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6586,6 +6751,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>ATACAND 8 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-982C90543DA9</t>
         </is>
       </c>
@@ -6609,7 +6779,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6770,6 +6940,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>ATACAND 32MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-F9F7C28BEA83</t>
         </is>
       </c>
@@ -6793,7 +6968,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6950,6 +7125,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>ATACAND 16 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-AB4AB338F027</t>
         </is>
       </c>
@@ -6973,7 +7153,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7128,6 +7308,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>APO-DOXY 100MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-04D4AD9E480B</t>
         </is>
       </c>
@@ -7151,7 +7336,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7310,6 +7495,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-C5AF54111BD0</t>
         </is>
       </c>
@@ -7333,7 +7523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7492,6 +7682,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-DF680FDBCF7C</t>
         </is>
       </c>
@@ -7515,7 +7710,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7678,6 +7873,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>ARBITEN 80MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-DD6D7BC09175</t>
         </is>
       </c>
@@ -7701,7 +7901,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7856,6 +8056,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ARBITEN 160MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-6E8CF34BCFA3</t>
         </is>
       </c>
@@ -7879,7 +8084,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8042,6 +8247,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-010B5F6E6669</t>
         </is>
       </c>
@@ -8065,7 +8275,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8224,6 +8434,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>ACULAR LS 0.4% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-BCF6A79920CD</t>
         </is>
       </c>
@@ -8247,7 +8462,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8402,6 +8617,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>ADOLIN 0.1% W-W GEL</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-90B406264E31</t>
         </is>
       </c>
@@ -8425,7 +8645,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8576,6 +8796,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>ALKA-UR EFFERVES. 4GM GRANULES SUGARFREE</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-335F87701635</t>
         </is>
       </c>
@@ -8599,7 +8824,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8762,6 +8987,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ALLERGODIL NASAL SPRAY WITH SPRAYER</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-36BC19C4D15A</t>
         </is>
       </c>
@@ -8785,7 +9015,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8940,6 +9170,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>AIRFAST 4MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-5EC60CBD7340</t>
         </is>
       </c>
@@ -8963,7 +9198,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9118,6 +9353,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>AIRFAST 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-978217C9EB4B</t>
         </is>
       </c>
@@ -9141,7 +9381,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9296,6 +9536,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>AIRFAST 5MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-85F80D8EC8E0</t>
         </is>
       </c>
@@ -9319,7 +9564,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9478,6 +9723,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>BRIMO-P OPHTHALMIC SOLUTION 0.1%</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-0EA683E95B50</t>
         </is>
       </c>
@@ -9501,7 +9751,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9660,6 +9910,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>CARTEOL LP 2% PRLONGED RELEASE EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-A03687460AE7</t>
         </is>
       </c>
@@ -9683,7 +9938,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9838,6 +10093,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>CARTEOL LP 1% PRLONGED RELEASE EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-8E80AB7B9088</t>
         </is>
       </c>
@@ -9861,7 +10121,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10020,6 +10280,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>CALSYR  SYRUP</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-A9FE40FAEE92</t>
         </is>
       </c>
@@ -10043,7 +10308,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10198,6 +10463,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>Avocom-M Cream</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-D1EB92F9E23D</t>
         </is>
       </c>
@@ -10221,7 +10491,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10380,6 +10650,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>Avocom-M Cream</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-76C3A94FC282</t>
         </is>
       </c>
@@ -10403,7 +10678,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10558,6 +10833,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>AVOGAIN</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-F61ED67E88C1</t>
         </is>
       </c>
@@ -10581,7 +10861,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10736,6 +11016,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>AVOGAIN</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-1366FB9617D4</t>
         </is>
       </c>
@@ -10759,7 +11044,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10918,6 +11203,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>BACTALL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-F37B951FE00D</t>
         </is>
       </c>
@@ -10941,7 +11231,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11096,6 +11386,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>BACTALL 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-440D925A6473</t>
         </is>
       </c>
@@ -11119,7 +11414,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11278,6 +11573,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>BACTRIM FORTE TAB</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-1F27BA62CD68</t>
         </is>
       </c>
@@ -11301,7 +11601,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11456,6 +11756,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>AVOCOM</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-62E8EA61D7B2</t>
         </is>
       </c>
@@ -11479,7 +11784,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11638,6 +11943,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>AVOCIN</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-95B1D72A4D36</t>
         </is>
       </c>
@@ -11661,7 +11971,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11816,6 +12126,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>AVOCIN</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-EC6441260C39</t>
         </is>
       </c>
@@ -11839,7 +12154,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -11998,6 +12313,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>AVAXIM 80U-0.5ML PEDIATRIC VACCINE</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-B1A3C704467E</t>
         </is>
       </c>
@@ -12021,7 +12341,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12176,6 +12496,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>BETADERM 0.1% cream</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-1C8438089C37</t>
         </is>
       </c>
@@ -12199,7 +12524,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12354,6 +12679,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>BEPANTHEN</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-00FE27E09B5B</t>
         </is>
       </c>
@@ -12377,7 +12707,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12540,6 +12870,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>BENZAC AC 5% GEL</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-37955449D40E</t>
         </is>
       </c>
@@ -12563,7 +12898,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12718,6 +13053,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>BETADERM 0.1% ointment</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-B6895B19FA7A</t>
         </is>
       </c>
@@ -12741,7 +13081,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12904,6 +13244,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>BETATEN 100MG F.C. TABS</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-588D8F3519CA</t>
         </is>
       </c>
@@ -12927,7 +13272,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13090,6 +13435,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>GLORA 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-2965B8B49C9E</t>
         </is>
       </c>
@@ -13113,7 +13463,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13274,6 +13624,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>GLUCOVANCE 2.5/500</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-C1D4777FFB4B</t>
         </is>
       </c>
@@ -13297,7 +13652,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13460,6 +13815,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>GLODIP 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-EC8FC94597C2</t>
         </is>
       </c>
@@ -13483,7 +13843,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13638,6 +13998,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>FUSIBACT-B CREAM</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-76150FFB838F</t>
         </is>
       </c>
@@ -13661,7 +14026,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13820,6 +14185,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>FUNZOL 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-F15F7A5E125B</t>
         </is>
       </c>
@@ -13843,7 +14213,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14002,6 +14372,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>GABANET 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-EC78C3D9EF56</t>
         </is>
       </c>
@@ -14025,7 +14400,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14184,6 +14559,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>GABANET 300MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-1B71D1A55235</t>
         </is>
       </c>
@@ -14207,7 +14587,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14366,6 +14746,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>FORTICEF 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-13B19FB007A2</t>
         </is>
       </c>
@@ -14389,7 +14774,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14548,6 +14933,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>FOSTIMON HP 75 IU VIAL (IM) USE</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-A0CD1B255134</t>
         </is>
       </c>
@@ -14571,7 +14961,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14730,6 +15120,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>FOSTIMON HP 150 IU VIAL IM(WOMEN URIN)</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-72EFF1E95649</t>
         </is>
       </c>
@@ -14753,7 +15148,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14914,6 +15309,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>GANFORT EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-C008F0B7ABA2</t>
         </is>
       </c>
@@ -14937,7 +15337,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15092,6 +15492,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>GLITRA 3MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-3969777D5DE4</t>
         </is>
       </c>
@@ -15115,7 +15520,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15270,6 +15675,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>GILENYA 0.5 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-A5D3BB0B448D</t>
         </is>
       </c>
@@ -15293,7 +15703,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15452,6 +15862,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>GAVISCON ADVANCE PEPPERMINT FLAVOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-DD5B5D167D45</t>
         </is>
       </c>
@@ -15475,7 +15890,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15636,6 +16051,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>GASEC 40MG GASTRO CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-581347105D10</t>
         </is>
       </c>
@@ -15659,7 +16079,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15820,6 +16240,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>GASEC 40MG GASTRO CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-5F296E7DD5AF</t>
         </is>
       </c>
@@ -15843,7 +16268,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16004,6 +16429,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>GASEC 20MG GASTRO CAPS</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-9D491C185C1F</t>
         </is>
       </c>
@@ -16027,7 +16457,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16188,6 +16618,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>GASEC 20MG GASTRO CAPS</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-B26DC44FE0B5</t>
         </is>
       </c>
@@ -16211,7 +16646,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16366,6 +16801,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>I-PROFEN 400MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-657B0F626F96</t>
         </is>
       </c>
@@ -16389,7 +16829,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16548,6 +16988,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>JOINT CARE MAX CAPSULES AND TABLETS</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-F3225AA7DCF2</t>
         </is>
       </c>
@@ -16571,7 +17016,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16726,6 +17171,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>IVARIN 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-03BA1664FE82</t>
         </is>
       </c>
@@ -16749,7 +17199,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16904,6 +17354,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>IVARIN 40MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-A1CAF7AA81F9</t>
         </is>
       </c>
@@ -16927,7 +17382,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17086,6 +17541,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>IVARIN 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-541314E13B3E</t>
         </is>
       </c>
@@ -17109,7 +17569,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17264,6 +17724,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>IVARIN 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-B163B2F646BE</t>
         </is>
       </c>
@@ -17287,7 +17752,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17446,6 +17911,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>KORANDIL</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-CE046CFF1D71</t>
         </is>
       </c>
@@ -17469,7 +17939,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17624,6 +18094,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>LACINE 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-F0887F529031</t>
         </is>
       </c>
@@ -17647,7 +18122,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17802,6 +18277,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>KETONIL 1MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-9BB609D50DD9</t>
         </is>
       </c>
@@ -17825,7 +18305,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -17976,6 +18456,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>KETOFAN 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-9D9ECF08E39C</t>
         </is>
       </c>
@@ -17999,7 +18484,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18162,6 +18647,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>KETESSE 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-1E5C63AAFBB6</t>
         </is>
       </c>
@@ -18185,7 +18675,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18340,6 +18830,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Zistan SYRUP</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-C16ED7FF9161</t>
         </is>
       </c>
@@ -18363,7 +18858,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18518,6 +19013,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Zistan 4 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-0665B4FF869F</t>
         </is>
       </c>
@@ -18541,7 +19041,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18695,6 +19195,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>INDERAL TABLETS 80 MG.</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-B6915273BF4D</t>
         </is>
@@ -18711,7 +19216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18757,100 +19262,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -18882,7 +19392,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18897,92 +19407,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-17671</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>38.97</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>630</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19014,7 +19529,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19029,92 +19544,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-18485</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>424.05</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>631</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19146,7 +19666,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19161,92 +19681,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-43031</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>199.35</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>632</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19278,7 +19803,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19293,92 +19818,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-56165</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>103.67</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>633</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19410,7 +19940,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19425,92 +19955,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-62035</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>141.67</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>634</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19542,7 +20077,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19557,92 +20092,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-62141</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>139.12</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>635</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19674,7 +20214,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19689,92 +20229,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-14068</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>405.36</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>636</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19806,7 +20351,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19821,92 +20366,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-31539</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>199.33</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>637</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19938,7 +20488,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -19953,92 +20503,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-23347</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>191.15</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>638</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20070,7 +20625,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20085,92 +20640,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-76231</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>337.59</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>639</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20202,7 +20762,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20217,92 +20777,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-88298</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>34.44</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>640</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20319,7 +20884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20425,6 +20990,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20460,7 +21035,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20525,6 +21100,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-85E72B9D78CF</t>
         </is>
@@ -20561,7 +21146,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20626,6 +21211,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-98BD8040831E</t>
         </is>
@@ -20662,7 +21257,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20727,6 +21322,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-1004A213DDE9</t>
         </is>
@@ -20763,7 +21368,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -20828,6 +21433,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-E1509C241355</t>
         </is>
@@ -20864,7 +21479,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -20929,6 +21544,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-A5F5880536EE</t>
         </is>
@@ -20965,7 +21590,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21030,6 +21655,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-E2A8DA3FC11D</t>
         </is>
@@ -21066,7 +21701,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21131,6 +21766,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-0C32FD574FB5</t>
         </is>
@@ -21167,7 +21812,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21232,6 +21877,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-A6A3467839A4</t>
         </is>
@@ -21268,7 +21923,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21333,6 +21988,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-D316AD8C7E86</t>
         </is>
@@ -21369,7 +22034,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21434,6 +22099,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-598CB5E18413</t>
         </is>
@@ -21470,7 +22145,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21535,6 +22210,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-BAB5D480E31F</t>
         </is>
@@ -21571,7 +22256,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21636,6 +22321,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-8A23E01D7F5E</t>
         </is>
@@ -21672,7 +22367,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21737,6 +22432,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-498AA3C64787</t>
         </is>
@@ -21773,7 +22478,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21838,6 +22543,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-2C853AB44651</t>
         </is>
@@ -21874,7 +22589,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -21939,6 +22654,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-CC3B4EA17A66</t>
         </is>
@@ -21975,7 +22700,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22040,6 +22765,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-85460BA234AA</t>
         </is>
@@ -22076,7 +22811,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22141,6 +22876,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-76FAC38DDB50</t>
         </is>
@@ -22177,7 +22922,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22242,6 +22987,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-02A3B4EC4C09</t>
         </is>
@@ -22278,7 +23033,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22343,6 +23098,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-A9F7481BDC31</t>
         </is>
@@ -22379,7 +23144,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22444,6 +23209,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-8C88C6250975</t>
         </is>

--- a/product_upload/packages/62/file.xlsx
+++ b/product_upload/packages/62/file.xlsx
@@ -686,8 +686,16 @@
           <t>5210190420-334-139856709178</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE .9% + DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE .9% + DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -873,8 +881,16 @@
           <t>9553868553-094-107976242306</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM ACETATE F.T.V.40mEq</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SODIUM ACETATE F.T.V.40mEq detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1064,8 +1080,16 @@
           <t>2164961414-490-925157003559</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLENIL FORTE 250MCG PUFF METERED INHALER</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CLENIL FORTE 250MCG PUFF METERED INHALER detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1243,8 +1267,16 @@
           <t>8640982456-193-202970445893</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLAVODAR 1GM F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CLAVODAR 1GM F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1430,8 +1462,16 @@
           <t>1912067106-540-588430921830</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLORACEF 250MG/5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CLORACEF 250MG/5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1617,8 +1657,16 @@
           <t>6912607411-110-238024680333</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITANEST 3% DENTAL OCTAPRESSIN CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CITANEST 3% DENTAL OCTAPRESSIN CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1804,8 +1852,16 @@
           <t>9782478698-866-293500116672</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITALOGEN 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CITALOGEN 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1987,8 +2043,16 @@
           <t>1861367275-088-648548332572</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITALOGEN 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CITALOGEN 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2170,8 +2234,16 @@
           <t>6607104714-753-785468673607</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARITINE 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CLARITINE 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2357,8 +2429,16 @@
           <t>2326265719-218-416687294388</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARITINE 10MG TAB</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CLARITINE 10MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2536,8 +2616,16 @@
           <t>1395847623-842-809669265176</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLORACEF 375MG- 5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CLORACEF 375MG- 5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2723,8 +2811,16 @@
           <t>0426887122-372-614529778545</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CONCOR 5 PLUS F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CONCOR 5 PLUS F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2914,8 +3010,16 @@
           <t>4269922139-969-389979341491</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CONCERTA EXTENDED RELEASE 36MG TABLET</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CONCERTA EXTENDED RELEASE 36MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3093,8 +3197,16 @@
           <t>3096412967-801-911980216245</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CONCERTA EXTENDED RELEASE 18MG TABLET</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CONCERTA EXTENDED RELEASE 18MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3276,8 +3388,16 @@
           <t>2076156731-340-451441896545</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COBAL 500MCG TAB</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>COBAL 500MCG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3455,8 +3575,16 @@
           <t>5286723776-368-454603925380</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COLI-URINAL effervescent granules</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>COLI-URINAL effervescent granules detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3634,8 +3762,16 @@
           <t>2462529461-344-041044339253</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFPROZ 250MG/5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CEFPROZ 250MG/5ML POWDER FOR ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3821,8 +3957,16 @@
           <t>8262872858-698-288223620517</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROCIN 0.3%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CIPROCIN 0.3% detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4008,8 +4152,16 @@
           <t>9736885670-178-301475934467</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROMAX 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CIPROMAX 500 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4195,8 +4347,16 @@
           <t>8180933249-416-743728456802</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPROMAX 750MG TAB</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CIPROMAX 750MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4374,8 +4534,16 @@
           <t>2552856329-451-403076357665</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CETROTIDE 0.25MG POW. FOR SOLU. FOR INJ.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CETROTIDE 0.25MG POW. FOR SOLU. FOR INJ. detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4561,8 +4729,16 @@
           <t>3195157725-631-788160621789</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CHORIOMON 5000 I.U VIAL+AMP OF SOLVENT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CHORIOMON 5000 I.U VIAL+AMP OF SOLVENT detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4752,8 +4928,16 @@
           <t>6273377956-950-921901751629</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CHLOROQUINE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CHLOROQUINE detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -4935,8 +5119,16 @@
           <t>8581005169-275-036399890916</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAROXIME</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>DAROXIME detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5122,8 +5314,16 @@
           <t>2692817445-645-161446215050</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DALACIN VAGINAL CREAM 2%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DALACIN VAGINAL CREAM 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5305,8 +5505,16 @@
           <t>8919765571-226-714442875393</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DALACIN T LOTION 1%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>DALACIN T LOTION 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5492,8 +5700,16 @@
           <t>6828677819-551-502617095692</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMATIN SOLUTION 1%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DERMATIN SOLUTION 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5675,8 +5891,16 @@
           <t>8595426672-890-061331993669</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMATIN CREAM 1%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>DERMATIN CREAM 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5862,8 +6086,16 @@
           <t>7764399177-179-251174006537</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMOVATE OINTMENT 0.05%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DERMOVATE OINTMENT 0.05% detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6045,8 +6277,16 @@
           <t>0452594746-898-003263680105</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DECAL B12</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>DECAL B12 detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6232,8 +6472,16 @@
           <t>8014352168-671-619017461619</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANTIPLATE 75MG TAB</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ANTIPLATE 75MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6415,8 +6663,16 @@
           <t>2245526453-843-512957801546</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOPINE 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>AMLOPINE 5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6598,8 +6854,16 @@
           <t>2557631112-102-179168907099</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATACAND 8 MG TAB</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ATACAND 8 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -6787,8 +7051,16 @@
           <t>6374454172-414-873505625245</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATACAND 32MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ATACAND 32MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -6976,8 +7248,16 @@
           <t>4600788135-160-400770044922</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATACAND 16 MG TAB</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ATACAND 16 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -7161,8 +7441,16 @@
           <t>5597840621-231-549147752535</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APO-DOXY 100MG CAPS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>APO-DOXY 100MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7344,8 +7632,16 @@
           <t>0312834471-001-660385944523</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ARBITEN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7531,8 +7827,16 @@
           <t>1804775186-371-904251392219</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ARBITEN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7718,8 +8022,16 @@
           <t>7831714571-581-297375678791</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN 80MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ARBITEN 80MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7909,8 +8221,16 @@
           <t>3170492233-239-915845688138</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN 160MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ARBITEN 160MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8092,8 +8412,16 @@
           <t>1235005922-449-301720577175</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ARBITEN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8283,8 +8611,16 @@
           <t>0309035001-828-506969927142</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACULAR LS 0.4% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACULAR LS 0.4% OPHTHALMIC SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8470,8 +8806,16 @@
           <t>5894463042-103-323632453736</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOLIN 0.1% W-W GEL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ADOLIN 0.1% W-W GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8653,8 +8997,16 @@
           <t>0897937775-519-312831010455</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALKA-UR EFFERVES. 4GM GRANULES SUGARFREE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ALKA-UR EFFERVES. 4GM GRANULES SUGARFREE detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -8832,8 +9184,16 @@
           <t>5352830923-148-032967190930</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERGODIL NASAL SPRAY WITH SPRAYER</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ALLERGODIL NASAL SPRAY WITH SPRAYER detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9023,8 +9383,16 @@
           <t>5532609538-751-463740940952</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AIRFAST 4MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>AIRFAST 4MG CHEWABLE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9206,8 +9574,16 @@
           <t>5554161222-280-482667844798</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AIRFAST 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>AIRFAST 10MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9389,8 +9765,16 @@
           <t>5288983301-124-626668559339</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AIRFAST 5MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>AIRFAST 5MG CHEWABLE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9572,8 +9956,16 @@
           <t>5701087777-868-131442979197</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIMO-P OPHTHALMIC SOLUTION 0.1%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>BRIMO-P OPHTHALMIC SOLUTION 0.1% detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9759,8 +10151,16 @@
           <t>4068251899-175-154821662803</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARTEOL LP 2% PRLONGED RELEASE EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CARTEOL LP 2% PRLONGED RELEASE EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -9946,8 +10346,16 @@
           <t>6337404462-961-735183927043</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARTEOL LP 1% PRLONGED RELEASE EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CARTEOL LP 1% PRLONGED RELEASE EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10129,8 +10537,16 @@
           <t>7317045447-449-196709173278</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALSYR  SYRUP</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CALSYR  SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10316,8 +10732,16 @@
           <t>3285908457-611-710636017358</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avocom-M Cream</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Avocom-M Cream detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10499,8 +10923,16 @@
           <t>8993159678-131-492566010706</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avocom-M Cream</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Avocom-M Cream detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10686,8 +11118,16 @@
           <t>3766251509-401-460943651081</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOGAIN</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>AVOGAIN detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10869,8 +11309,16 @@
           <t>1096412836-845-007152259473</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOGAIN</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>AVOGAIN detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11052,8 +11500,16 @@
           <t>1618562639-334-051203083646</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BACTALL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>BACTALL 500MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11239,8 +11695,16 @@
           <t>5051246564-307-451957799666</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BACTALL 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>BACTALL 250MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11422,8 +11886,16 @@
           <t>5535364067-125-588891945208</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BACTRIM FORTE TAB</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>BACTRIM FORTE TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11609,8 +12081,16 @@
           <t>9707487575-501-994402668828</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOCOM</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>AVOCOM detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11792,8 +12272,16 @@
           <t>6151549477-977-966905942764</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOCIN</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>AVOCIN detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -11979,8 +12467,16 @@
           <t>0590834542-116-621685550110</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOCIN</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>AVOCIN detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12162,8 +12658,16 @@
           <t>7770405572-873-524897785315</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVAXIM 80U-0.5ML PEDIATRIC VACCINE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>AVAXIM 80U-0.5ML PEDIATRIC VACCINE detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12349,8 +12853,16 @@
           <t>9640943380-774-058208618925</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETADERM 0.1% cream</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>BETADERM 0.1% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12532,8 +13044,16 @@
           <t>7366039246-584-397645068853</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BEPANTHEN</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>BEPANTHEN detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12715,8 +13235,16 @@
           <t>6371744500-409-182039033311</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BENZAC AC 5% GEL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>BENZAC AC 5% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -12906,8 +13434,16 @@
           <t>2514355053-298-149305954753</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETADERM 0.1% ointment</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>BETADERM 0.1% ointment detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13089,8 +13625,16 @@
           <t>0931643916-931-352854936015</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETATEN 100MG F.C. TABS</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>BETATEN 100MG F.C. TABS detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13280,8 +13824,16 @@
           <t>8697237379-541-935529210905</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLORA 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>GLORA 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13471,8 +14023,16 @@
           <t>4640602824-240-657820298299</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLUCOVANCE 2.5/500</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>GLUCOVANCE 2.5/500 detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>RIYADH PHARMA</t>
@@ -13660,8 +14220,16 @@
           <t>2356804159-551-689532805348</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLODIP 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>GLODIP 5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -13851,8 +14419,16 @@
           <t>8162422519-524-439092882964</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUSIBACT-B CREAM</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>FUSIBACT-B CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14034,8 +14610,16 @@
           <t>0573399802-313-193950898803</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUNZOL 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>FUNZOL 150MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14221,8 +14805,16 @@
           <t>4273342684-523-417856933799</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABANET 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>GABANET 400MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14408,8 +15000,16 @@
           <t>0939567741-278-691716672844</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABANET 300MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>GABANET 300MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14595,8 +15195,16 @@
           <t>9463752690-528-058072335283</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FORTICEF 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>FORTICEF 500MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14782,8 +15390,16 @@
           <t>0342616007-864-545106993056</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FOSTIMON HP 75 IU VIAL (IM) USE</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>FOSTIMON HP 75 IU VIAL (IM) USE detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -14969,8 +15585,16 @@
           <t>9801383544-255-144126160349</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FOSTIMON HP 150 IU VIAL IM(WOMEN URIN)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>FOSTIMON HP 150 IU VIAL IM(WOMEN URIN) detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15156,8 +15780,16 @@
           <t>9675223773-072-070198421434</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GANFORT EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>GANFORT EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -15345,8 +15977,16 @@
           <t>4094228242-938-128016747893</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLITRA 3MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>GLITRA 3MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15528,8 +16168,16 @@
           <t>9271631013-416-243972245260</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GILENYA 0.5 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>GILENYA 0.5 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -15711,8 +16359,16 @@
           <t>5488730730-680-584623956356</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAVISCON ADVANCE PEPPERMINT FLAVOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>GAVISCON ADVANCE PEPPERMINT FLAVOR ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -15898,8 +16554,16 @@
           <t>1446711998-471-107534648035</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GASEC 40MG GASTRO CAPSULES</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>GASEC 40MG GASTRO CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -16087,8 +16751,16 @@
           <t>8117377248-743-493283012032</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GASEC 40MG GASTRO CAPSULES</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>GASEC 40MG GASTRO CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -16276,8 +16948,16 @@
           <t>4901295244-016-978640665673</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GASEC 20MG GASTRO CAPS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>GASEC 20MG GASTRO CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -16465,8 +17145,16 @@
           <t>8446209180-242-828743678328</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GASEC 20MG GASTRO CAPS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>GASEC 20MG GASTRO CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -16654,8 +17342,16 @@
           <t>2943473544-584-790551222186</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ I-PROFEN 400MG TABLET</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>I-PROFEN 400MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -16837,8 +17533,16 @@
           <t>7082211188-538-970943623518</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JOINT CARE MAX CAPSULES AND TABLETS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>JOINT CARE MAX CAPSULES AND TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17024,8 +17728,16 @@
           <t>6557776591-408-268981013465</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IVARIN 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>IVARIN 5MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17207,8 +17919,16 @@
           <t>7594297814-082-300739681502</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IVARIN 40MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>IVARIN 40MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17390,8 +18110,16 @@
           <t>7674709235-837-813181558521</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IVARIN 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>IVARIN 20MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17577,8 +18305,16 @@
           <t>0340723440-485-711409349157</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IVARIN 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>IVARIN 10MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17760,8 +18496,16 @@
           <t>4383089576-392-623923439306</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KORANDIL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>KORANDIL detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -17947,8 +18691,16 @@
           <t>1389456275-901-911657290898</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LACINE 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>LACINE 50MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18130,8 +18882,16 @@
           <t>6418622294-539-440279673599</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KETONIL 1MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>KETONIL 1MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18313,8 +19073,16 @@
           <t>2200630385-641-447506291913</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KETOFAN 25MG TAB</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>KETOFAN 25MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18492,8 +19260,16 @@
           <t>9662894133-308-352419226537</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KETESSE 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>KETESSE 25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18683,8 +19459,16 @@
           <t>1446694805-386-452448527458</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zistan SYRUP</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Zistan SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -18866,8 +19650,16 @@
           <t>3489425086-660-419023489281</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zistan 4 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Zistan 4 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19049,8 +19841,16 @@
           <t>0662602631-537-292638638873</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INDERAL TABLETS 80 MG.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>INDERAL TABLETS 80 MG. detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/62/file.xlsx
+++ b/product_upload/packages/62/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20062,7 +20062,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21684,7 +21684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21765,40 +21765,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21878,38 +21883,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>441.8</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-85E72B9D78CF</t>
         </is>
@@ -21989,38 +21999,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>320</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-98BD8040831E</t>
         </is>
@@ -22100,38 +22115,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>195.56</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-1004A213DDE9</t>
         </is>
@@ -22211,38 +22231,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>441.6</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-E1509C241355</t>
         </is>
@@ -22322,38 +22347,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>53</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-A5F5880536EE</t>
         </is>
@@ -22433,38 +22463,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>227.68</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-E2A8DA3FC11D</t>
         </is>
@@ -22544,38 +22579,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>32.96</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-0C32FD574FB5</t>
         </is>
@@ -22655,38 +22695,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>288.39</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-A6A3467839A4</t>
         </is>
@@ -22766,38 +22811,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>445.57</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-D316AD8C7E86</t>
         </is>
@@ -22877,38 +22927,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>181.86</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-598CB5E18413</t>
         </is>
@@ -22988,38 +23043,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>435.82</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-BAB5D480E31F</t>
         </is>
@@ -23099,38 +23159,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>495.86</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-8A23E01D7F5E</t>
         </is>
@@ -23210,38 +23275,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>285.51</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-498AA3C64787</t>
         </is>
@@ -23321,38 +23391,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>100.04</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-2C853AB44651</t>
         </is>
@@ -23432,38 +23507,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>148.04</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-CC3B4EA17A66</t>
         </is>
@@ -23543,38 +23623,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>40.14</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-85460BA234AA</t>
         </is>
@@ -23654,38 +23739,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>260.46</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-76FAC38DDB50</t>
         </is>
@@ -23765,38 +23855,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>409.45</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-02A3B4EC4C09</t>
         </is>
@@ -23876,38 +23971,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>82.91</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-A9F7481BDC31</t>
         </is>
@@ -23987,38 +24087,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>367.06</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-8C88C6250975</t>
         </is>
